--- a/eit_output_v3/038012_2A_preprocessed/transcriptions/transcriptions.xlsx
+++ b/eit_output_v3/038012_2A_preprocessed/transcriptions/transcriptions.xlsx
@@ -36,7 +36,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +55,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
+        <fgColor rgb="0090EE90"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -105,6 +110,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -545,20 +553,20 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Quiero cortarle la cara.</t>
+          <t>quiero cortar</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
         <v>0.75</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.3043</v>
+        <v>0.4348</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.3</v>
@@ -580,14 +588,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>El libro está a la mesa.</t>
+          <t>El libro está en la mesa</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>6</v>
@@ -650,14 +658,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Él se duche cada mañana.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0.08699999999999999</v>
+          <t>él se ducha cada mañana</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>5</v>
@@ -755,7 +763,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>La calle Sente... Los calles...</t>
+          <t>La calle Sentee Los calles Andes</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -768,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>6.2</v>
@@ -790,7 +798,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>El pueblo se quiere llegar.</t>
+          <t>El pueblo se quiere ir a calle</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -803,7 +811,7 @@
         <v>7</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.3</v>
@@ -825,13 +833,13 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Las casas son bonitas pero caras.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
+          <t>las casas son bonitas pero caras</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>0.1429</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="6" t="n">
         <v>0.1111</v>
       </c>
       <c r="F10" s="2" t="n">
@@ -860,20 +868,20 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Me gustan las películas, pecan bien.</t>
+          <t>me gustan las películas que acaban bien</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.2857</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.1</v>
@@ -895,20 +903,20 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>El chico es... ...bonario... ...es español.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.359</v>
+          <t>el chico es un bonal yo es español</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3077</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>5.3</v>
@@ -930,7 +938,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Después llegar, dormir.</t>
+          <t>después llegar, dormir</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -965,14 +973,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Quiero la casa, está, a mí animales.</t>
+          <t>Quiero la casa esta a mi animales</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
         <v>0.6667</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.3636</v>
+        <v>0.3182</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>9</v>
@@ -1000,20 +1008,20 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>A nosotros, a las nabas, a los nosotros.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.5</v>
+          <t>A nosotros nos fascinan los nosotros</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3261</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>4.8</v>
@@ -1035,20 +1043,20 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Es el conversio del domingo.</t>
+          <t>es el converse y nos del</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.6757</v>
+        <v>0.6486</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>6.5</v>
@@ -1070,7 +1078,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Me gustaría que los besos Vestas Ya</t>
+          <t>me gustaría que los pesos bestia</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1083,7 +1091,7 @@
         <v>9</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6.4</v>
@@ -1105,7 +1113,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cruzar a la derecha.</t>
+          <t>cruzar a la derecha</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1140,14 +1148,14 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>He terminado el esplendor.</t>
+          <t>He terminado el apartamento</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.8571</v>
+        <v>0.7143</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.5952</v>
+        <v>0.4048</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>7</v>
@@ -1175,7 +1183,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Me gustaría hacer pingatas esta... gustaría pronto.</t>
+          <t>me gustaría hacer pingatas esta... gustaría pronto</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1210,20 +1218,20 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>El niño, el niño sirio gato es tan muy triste.</t>
+          <t>el niño sirio gato es tan muy triste</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>0.7272999999999999</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.4783</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>5.6</v>
@@ -1245,7 +1253,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Una amiga picado en mi vecino.</t>
+          <t>una amiga picado en mi vecino</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1280,20 +1288,20 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>El gato sin señal negro y el lapero.</t>
+          <t>el gato se llenó de señas negras y el perro</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.5102</v>
+        <v>0.4898</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>6.5</v>
@@ -1315,14 +1323,14 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>¿Qué es limpiar tus cuartos?</t>
+          <t>que se limpiar tus cuartos</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.6471</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>10</v>
@@ -1350,20 +1358,20 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>La cantina de la ley es afortunada por su más.</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>0.617</v>
+          <t>La cantidad de personas que han sido asesinadas</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.3191</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>5.5</v>
@@ -1385,7 +1393,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Después de llegar a mi casa, voy a la cena.</t>
+          <t>después de llegar a mi casa voy a la cena</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -1420,20 +1428,20 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>...de si era fomo, o sea...</t>
+          <t>la policía era famoso</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>0.5556</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.7778</v>
+        <v>0.5333</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.7</v>
@@ -1455,14 +1463,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>La vida es una mega.</t>
+          <t>le pedí de una amiga</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>0.8182</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.7391</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>11</v>
@@ -1490,7 +1498,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Esta tarea es difícil para la derecha.</t>
+          <t>esta tarea es difícil para la derecha</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -1525,14 +1533,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>¿Qué está en la mesa? La es... de libro... ...es, ehm, son...</t>
+          <t>¿Qué está en la mesa? ¿La es... de libro? ¿Som... santa nena?</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.6545</v>
+        <v>0.6182</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>12</v>
@@ -1603,7 +1611,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Recording</t>
         </is>
@@ -1615,7 +1623,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
@@ -1627,7 +1635,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
@@ -1639,7 +1647,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
@@ -1651,7 +1659,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Total stimuli</t>
         </is>
@@ -1663,7 +1671,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Transcribed</t>
         </is>
@@ -1675,7 +1683,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
@@ -1687,7 +1695,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Silence</t>
         </is>
@@ -1699,38 +1707,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Mean WER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>62.6%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Median WER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Mean CER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>

--- a/eit_output_v3/038012_2A_preprocessed/transcriptions/transcriptions.xlsx
+++ b/eit_output_v3/038012_2A_preprocessed/transcriptions/transcriptions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Transcriptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transcriptions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,7 +50,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF6961"/>
+        <fgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
     <fill>
@@ -60,12 +60,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFA500"/>
+        <fgColor rgb="00FF6961"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
+        <fgColor rgb="00FFA500"/>
       </patternFill>
     </fill>
   </fills>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -493,6 +493,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,6 +542,11 @@
           <t>ASR STATUS</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DRIFT CORRECTED</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -553,20 +559,20 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>quiero cortar</t>
+          <t>Quiero cortarme el...</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.4348</v>
+        <v>0.2174</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1.3</v>
@@ -575,6 +581,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J2" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -611,6 +620,9 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="J3" s="2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -623,20 +635,20 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>El carro lo tiene a pelo.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.1739</v>
+          <t>El carro lo tiene Pedro</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1.6</v>
@@ -645,6 +657,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J4" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -658,20 +673,20 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>él se ducha cada mañana</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0.0435</v>
+          <t>El seduce cara mañana.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.1739</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1.8</v>
@@ -680,6 +695,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J5" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -693,14 +711,14 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>¿Qué dice ese que pasa, héroe?</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.3333</v>
+          <t>¿Quién hizo ese que pasé hoy?</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5152</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>8</v>
@@ -715,6 +733,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -728,20 +749,20 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>duro secalesar también</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
+          <t>Duros de calizar también</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>0.5333</v>
+      <c r="E7" s="5" t="n">
+        <v>0.5667</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>3.9</v>
@@ -750,6 +771,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J7" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -763,14 +787,14 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>La calle Sentee Los calles Andes</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.6</v>
+          <t>Las calles son de... Los calles.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.525</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>8</v>
@@ -785,6 +809,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J8" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -798,20 +825,20 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>El pueblo se quiere ir a calle</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.7714</v>
+          <t>Puede que haya que seguir en la calle</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6857</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>2.3</v>
@@ -820,6 +847,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J9" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -833,13 +863,13 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>las casas son bonitas pero caras</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
+          <t>Las casas son bonitas pero caras</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>0.1429</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="3" t="n">
         <v>0.1111</v>
       </c>
       <c r="F10" s="2" t="n">
@@ -855,6 +885,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J10" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -868,20 +901,20 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>me gustan las películas que acaban bien</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
+          <t>Me gustan las películas pecar bien</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.1795</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>3.1</v>
@@ -890,6 +923,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J11" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -903,20 +939,20 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>el chico es un bonal yo es español</t>
+          <t>El chico es un ponalio es español</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.4444</v>
+        <v>0.5556</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.3077</v>
+        <v>0.2821</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>5.3</v>
@@ -925,6 +961,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J12" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -938,20 +977,20 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>después llegar, dormir</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0.5714</v>
+          <t>Después de llegar a dormir</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.4762</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>6.5</v>
@@ -960,6 +999,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J13" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -973,14 +1015,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Quiero la casa esta a mi animales</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0.3182</v>
+          <t>Quiero la casa estar a mis animales</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.2955</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>9</v>
@@ -995,6 +1037,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J14" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1008,14 +1053,14 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>A nosotros nos fascinan los nosotros</t>
+          <t>A nosotros fascinamos a los nosotros.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.4286</v>
+        <v>0.7143</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.3261</v>
+        <v>0.4783</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>7</v>
@@ -1030,6 +1075,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J15" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1043,20 +1091,20 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>es el converse y nos del</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
+          <t>Ella es el conversino del...</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>0.875</v>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>0.6486</v>
+      <c r="E16" s="5" t="n">
+        <v>0.5946</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>6.5</v>
@@ -1065,6 +1113,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J16" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1078,20 +1129,20 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>me gustaría que los pesos bestia</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
+          <t>Me gustaría que los precios bestas ya</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>0.6667</v>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>0.4444</v>
+      <c r="E17" s="5" t="n">
+        <v>0.3778</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6.4</v>
@@ -1100,6 +1151,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J17" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1113,13 +1167,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>cruzar a la derecha</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
+          <t>Cruzar a la derecha</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>0.6667</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="5" t="n">
         <v>0.6222</v>
       </c>
       <c r="F18" s="2" t="n">
@@ -1135,6 +1189,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J18" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1148,20 +1205,20 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>He terminado el apartamento</t>
+          <t>Ella ha terminado de espasar su apartamento</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.7143</v>
+        <v>0.1429</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.4048</v>
+        <v>0.119</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>5.8</v>
@@ -1170,6 +1227,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J19" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1183,13 +1243,13 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>me gustaría hacer pingatas esta... gustaría pronto</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
+          <t>Me gustaría hacer pincaz, esta gustaría pronto</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
         <v>0.6667</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="5" t="n">
         <v>0.4898</v>
       </c>
       <c r="F20" s="2" t="n">
@@ -1205,6 +1265,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J20" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1218,20 +1281,20 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>el niño sirio gato es tan muy triste</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
+          <t>El niño, el niño ciriocato es tan muy triste</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>0.7272999999999999</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="5" t="n">
         <v>0.5217000000000001</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>5.6</v>
@@ -1240,6 +1303,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J21" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1253,13 +1319,13 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>una amiga picado en mi vecino</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
+          <t>Una amiga picado en mi vecino</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="5" t="n">
         <v>0.4545</v>
       </c>
       <c r="F22" s="2" t="n">
@@ -1275,6 +1341,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J22" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1288,20 +1357,20 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>el gato se llenó de señas negras y el perro</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E23" s="3" t="n">
+          <t>El gato sin niña negro y el perro</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="6" t="n">
         <v>0.4898</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>6.5</v>
@@ -1310,6 +1379,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J23" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1323,20 +1395,20 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>que se limpiar tus cuartos</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>0.6274999999999999</v>
+          <t>¿Qué es el limpiar tu cuarto?</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.5686</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>2.7</v>
@@ -1345,6 +1417,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J24" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1358,20 +1433,20 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>La cantidad de personas que han sido asesinadas</t>
+          <t>La cantona de laia es una persona más personal.</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.375</v>
+        <v>0.875</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.3191</v>
+        <v>0.6596</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>5.5</v>
@@ -1380,6 +1455,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J25" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1393,13 +1471,13 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>después de llegar a mi casa voy a la cena</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
+          <t>Después de llegar a mi casa, voy a la cena</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="6" t="n">
         <v>0.3469</v>
       </c>
       <c r="F26" s="2" t="n">
@@ -1415,6 +1493,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J26" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1428,20 +1509,20 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>la policía era famoso</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0.5333</v>
+          <t>y si ya era a forma de una sola.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.7111</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>1.7</v>
@@ -1450,6 +1531,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J27" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1463,14 +1547,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>le pedí de una amiga</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0.8182</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>0.6739000000000001</v>
+          <t>Le pedí a una amiga</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.7272999999999999</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.6304</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>11</v>
@@ -1485,6 +1569,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J28" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1498,20 +1585,20 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>esta tarea es difícil para la derecha</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>0.6531</v>
+          <t>Estar a la ruta es tan difícil para estar a la ruta</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.6327</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>4.8</v>
@@ -1520,6 +1607,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J29" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1533,20 +1623,20 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>¿Qué está en la mesa? ¿La es... de libro? ¿Som... santa nena?</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>0.6182</v>
+          <t>¿Qué está en la mesa? ¿Qué está en la mesa? ¿Qué está en la mesa?</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.5636</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>12</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>8</v>
@@ -1555,6 +1645,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J30" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1568,14 +1661,14 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Hay muchos ejemplos, pero...</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
+          <t>Hay mucho ejemplo pero...</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>0.6939</v>
+      <c r="E31" s="5" t="n">
+        <v>0.6735</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>10</v>
@@ -1590,6 +1683,9 @@
         <is>
           <t>OK</t>
         </is>
+      </c>
+      <c r="J31" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1603,7 +1699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1630,7 +1726,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>whisper-large-v3</t>
+          <t>whisper-small</t>
         </is>
       </c>
     </row>
@@ -1709,36 +1805,48 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Mean WER</t>
+          <t>Drift corrected</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Median WER</t>
+          <t>Mean WER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>61.4%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>Median WER</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>Mean CER</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>43.6%</t>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
